--- a/tests/fixtures/manual_spill_cache/copy_partial.xlsx
+++ b/tests/fixtures/manual_spill_cache/copy_partial.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\manual_spill_cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E48BC240-9523-47B7-8A07-F32FB00569AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0BEDB61-FA98-453E-8DA3-FA6ED7F3CCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{A559D729-C84B-4958-B1C4-432D20AFB6AD}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{790BA775-9034-470A-A72B-150449CC3C2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFB89FD-607E-401F-958E-6E0086274FFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C919135-781E-4094-998D-E1C0A4867E83}">
   <dimension ref="B2:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -470,7 +470,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0528F1-BD07-4086-88C6-D8F2E1BE65F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{532EBE6C-24BC-4CD9-8FB6-E699F9BA3187}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
